--- a/artfynd/A 11031-2025 artfynd.xlsx
+++ b/artfynd/A 11031-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,6 +922,127 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132991981</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56895</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Blötområdet, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>694627</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6637228</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På vägen</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11031-2025 artfynd.xlsx
+++ b/artfynd/A 11031-2025 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>132991981</v>
       </c>
       <c r="B4" t="n">
-        <v>56895</v>
+        <v>56898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
